--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/21.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/21.xlsx
@@ -426,13 +426,13 @@
         <v>-14.96509617951326</v>
       </c>
       <c r="E2">
-        <v>-9.114493411263783</v>
+        <v>-10.86655094788343</v>
       </c>
       <c r="F2">
-        <v>-6.330706902728421</v>
+        <v>-6.266262403892829</v>
       </c>
       <c r="G2">
-        <v>-6.746532110239232</v>
+        <v>-8.282760972828173</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.14875099606343</v>
       </c>
       <c r="E3">
-        <v>-9.801548959233523</v>
+        <v>-11.14512908341329</v>
       </c>
       <c r="F3">
-        <v>-6.009543890458636</v>
+        <v>-6.17468555914594</v>
       </c>
       <c r="G3">
-        <v>-6.856385942868869</v>
+        <v>-7.924149437832162</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.57589014746156</v>
       </c>
       <c r="E4">
-        <v>-10.62489346093811</v>
+        <v>-11.26975721657838</v>
       </c>
       <c r="F4">
-        <v>-6.287862912288229</v>
+        <v>-5.683425584385304</v>
       </c>
       <c r="G4">
-        <v>-6.672382511250636</v>
+        <v>-8.392376446178982</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.99454880416593</v>
       </c>
       <c r="E5">
-        <v>-11.51581638025916</v>
+        <v>-12.13888006202651</v>
       </c>
       <c r="F5">
-        <v>-6.088525408845958</v>
+        <v>-5.799720084064327</v>
       </c>
       <c r="G5">
-        <v>-6.798812245395403</v>
+        <v>-7.810362677101871</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-20.34524397056304</v>
       </c>
       <c r="E6">
-        <v>-11.49612657527381</v>
+        <v>-12.90174226488465</v>
       </c>
       <c r="F6">
-        <v>-6.234403393581159</v>
+        <v>-5.612161136722463</v>
       </c>
       <c r="G6">
-        <v>-7.446775392160335</v>
+        <v>-8.135501286150312</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-21.49781364895092</v>
       </c>
       <c r="E7">
-        <v>-11.67998261998522</v>
+        <v>-13.3777392247789</v>
       </c>
       <c r="F7">
-        <v>-5.838288041971269</v>
+        <v>-5.522610478642823</v>
       </c>
       <c r="G7">
-        <v>-6.658594089079572</v>
+        <v>-8.269465821942461</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-22.35672262012079</v>
       </c>
       <c r="E8">
-        <v>-12.45892996251861</v>
+        <v>-13.15505604392571</v>
       </c>
       <c r="F8">
-        <v>-5.918533649015263</v>
+        <v>-5.59873247275568</v>
       </c>
       <c r="G8">
-        <v>-7.05110892094326</v>
+        <v>-7.756116077895374</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-22.81363086539079</v>
       </c>
       <c r="E9">
-        <v>-13.61395801444101</v>
+        <v>-14.59360279652033</v>
       </c>
       <c r="F9">
-        <v>-5.483007061482381</v>
+        <v>-5.43370429040256</v>
       </c>
       <c r="G9">
-        <v>-6.916876230962432</v>
+        <v>-8.714658054427032</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-22.80424118170426</v>
       </c>
       <c r="E10">
-        <v>-13.68123755277296</v>
+        <v>-15.03682719002107</v>
       </c>
       <c r="F10">
-        <v>-5.343100777353961</v>
+        <v>-5.173523201224666</v>
       </c>
       <c r="G10">
-        <v>-6.881810932610471</v>
+        <v>-8.166348949485242</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-22.28761713621896</v>
       </c>
       <c r="E11">
-        <v>-14.52244688443781</v>
+        <v>-16.2937776064341</v>
       </c>
       <c r="F11">
-        <v>-5.336984940819092</v>
+        <v>-4.978964549329146</v>
       </c>
       <c r="G11">
-        <v>-6.683227858437289</v>
+        <v>-8.634258145460292</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-21.27206299555977</v>
       </c>
       <c r="E12">
-        <v>-14.95598940051015</v>
+        <v>-15.37794355159686</v>
       </c>
       <c r="F12">
-        <v>-5.261187666728132</v>
+        <v>-4.847138160847633</v>
       </c>
       <c r="G12">
-        <v>-5.816791879899234</v>
+        <v>-7.620880292616146</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-19.79939948299969</v>
       </c>
       <c r="E13">
-        <v>-15.7502656275595</v>
+        <v>-16.88853832565351</v>
       </c>
       <c r="F13">
-        <v>-5.167193645899875</v>
+        <v>-4.862144864716749</v>
       </c>
       <c r="G13">
-        <v>-5.923500694266562</v>
+        <v>-7.359933161574173</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-17.96111719708091</v>
       </c>
       <c r="E14">
-        <v>-16.74570572697758</v>
+        <v>-17.25408580450068</v>
       </c>
       <c r="F14">
-        <v>-4.647661491681692</v>
+        <v>-4.32963882023592</v>
       </c>
       <c r="G14">
-        <v>-5.716300270054657</v>
+        <v>-6.925950436285574</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.87562457207972</v>
       </c>
       <c r="E15">
-        <v>-16.01041740235214</v>
+        <v>-16.24642335373589</v>
       </c>
       <c r="F15">
-        <v>-4.562574905535739</v>
+        <v>-4.103717350103008</v>
       </c>
       <c r="G15">
-        <v>-5.607836866551515</v>
+        <v>-6.846874745534542</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.68482875660471</v>
       </c>
       <c r="E16">
-        <v>-16.72131083749826</v>
+        <v>-17.67512520383784</v>
       </c>
       <c r="F16">
-        <v>-4.307887548973211</v>
+        <v>-4.154040669823078</v>
       </c>
       <c r="G16">
-        <v>-4.894679146481716</v>
+        <v>-6.593508763777501</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.53143036541234</v>
       </c>
       <c r="E17">
-        <v>-17.06597299422205</v>
+        <v>-18.60068642084356</v>
       </c>
       <c r="F17">
-        <v>-4.272093793498244</v>
+        <v>-3.707690633805218</v>
       </c>
       <c r="G17">
-        <v>-3.936852247786541</v>
+        <v>-5.812918541618287</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.54902819635387</v>
       </c>
       <c r="E18">
-        <v>-17.84924955790677</v>
+        <v>-19.45967454146252</v>
       </c>
       <c r="F18">
-        <v>-3.631662245208876</v>
+        <v>-3.105803849135514</v>
       </c>
       <c r="G18">
-        <v>-3.992128426655751</v>
+        <v>-5.915363373331034</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.845540942155499</v>
       </c>
       <c r="E19">
-        <v>-19.53390528739625</v>
+        <v>-19.30710572367009</v>
       </c>
       <c r="F19">
-        <v>-3.483648729309258</v>
+        <v>-2.93955548159807</v>
       </c>
       <c r="G19">
-        <v>-3.327529788555982</v>
+        <v>-5.895311398999667</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.494043364241276</v>
       </c>
       <c r="E20">
-        <v>-20.49044126661444</v>
+        <v>-20.77402789439678</v>
       </c>
       <c r="F20">
-        <v>-2.926924535440183</v>
+        <v>-2.857447704632583</v>
       </c>
       <c r="G20">
-        <v>-4.531896324106222</v>
+        <v>-6.608164548879854</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.529830473994859</v>
       </c>
       <c r="E21">
-        <v>-19.74029501876983</v>
+        <v>-21.96507995705019</v>
       </c>
       <c r="F21">
-        <v>-2.815974662244023</v>
+        <v>-2.010426296289435</v>
       </c>
       <c r="G21">
-        <v>-4.40394704955893</v>
+        <v>-6.183702952562199</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.952932195682209</v>
       </c>
       <c r="E22">
-        <v>-20.21661802879263</v>
+        <v>-22.10020509296506</v>
       </c>
       <c r="F22">
-        <v>-2.68875565325688</v>
+        <v>-2.053101299779457</v>
       </c>
       <c r="G22">
-        <v>-4.31686977023948</v>
+        <v>-6.103336149050851</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.746994298380039</v>
       </c>
       <c r="E23">
-        <v>-20.26892643205523</v>
+        <v>-22.44623937731318</v>
       </c>
       <c r="F23">
-        <v>-2.879842617367268</v>
+        <v>-1.990673047202278</v>
       </c>
       <c r="G23">
-        <v>-4.326188955932529</v>
+        <v>-6.022062256061743</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.87081333896515</v>
       </c>
       <c r="E24">
-        <v>-21.54918490418574</v>
+        <v>-23.00295638639415</v>
       </c>
       <c r="F24">
-        <v>-1.896147214501424</v>
+        <v>-1.59806168970623</v>
       </c>
       <c r="G24">
-        <v>-4.689683545598966</v>
+        <v>-5.894387756794211</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.270640659134575</v>
       </c>
       <c r="E25">
-        <v>-21.69618369894873</v>
+        <v>-22.7456349078563</v>
       </c>
       <c r="F25">
-        <v>-2.24610427769252</v>
+        <v>-1.916144003605004</v>
       </c>
       <c r="G25">
-        <v>-4.461792211766616</v>
+        <v>-6.997514499207999</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.877385371393711</v>
       </c>
       <c r="E26">
-        <v>-22.67283063123498</v>
+        <v>-22.46450724146012</v>
       </c>
       <c r="F26">
-        <v>-2.062439485511216</v>
+        <v>-1.619895797709219</v>
       </c>
       <c r="G26">
-        <v>-4.885263954968028</v>
+        <v>-6.472432181769736</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.625831830966136</v>
       </c>
       <c r="E27">
-        <v>-22.28480833588775</v>
+        <v>-23.13657354046447</v>
       </c>
       <c r="F27">
-        <v>-1.989141395874502</v>
+        <v>-1.609722617635439</v>
       </c>
       <c r="G27">
-        <v>-6.143625488263782</v>
+        <v>-6.98043208422536</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.44940119978231</v>
       </c>
       <c r="E28">
-        <v>-22.45350757809549</v>
+        <v>-23.35105565488976</v>
       </c>
       <c r="F28">
-        <v>-1.784380571046103</v>
+        <v>-1.856498237133828</v>
       </c>
       <c r="G28">
-        <v>-5.98642423333149</v>
+        <v>-6.891553868132546</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.292312950369297</v>
       </c>
       <c r="E29">
-        <v>-22.79560661853094</v>
+        <v>-22.56589524601785</v>
       </c>
       <c r="F29">
-        <v>-1.814069258762437</v>
+        <v>-1.732570331838008</v>
       </c>
       <c r="G29">
-        <v>-5.453188042230001</v>
+        <v>-6.104229996346454</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.1030221586891</v>
       </c>
       <c r="E30">
-        <v>-22.31499514362288</v>
+        <v>-23.48008999326432</v>
       </c>
       <c r="F30">
-        <v>-2.058366402991651</v>
+        <v>-1.795399514238142</v>
       </c>
       <c r="G30">
-        <v>-5.758652079138553</v>
+        <v>-7.036443204204289</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.841363741420967</v>
       </c>
       <c r="E31">
-        <v>-22.1661759023088</v>
+        <v>-23.30406820858617</v>
       </c>
       <c r="F31">
-        <v>-2.260734074393361</v>
+        <v>-2.203211413575561</v>
       </c>
       <c r="G31">
-        <v>-6.279917337570037</v>
+        <v>-6.385848173735637</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.48180711143745</v>
       </c>
       <c r="E32">
-        <v>-21.68744827258793</v>
+        <v>-22.85152421557765</v>
       </c>
       <c r="F32">
-        <v>-2.353961027006627</v>
+        <v>-2.304073428540429</v>
       </c>
       <c r="G32">
-        <v>-6.150071120428743</v>
+        <v>-6.285247315888264</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.01452822453563</v>
       </c>
       <c r="E33">
-        <v>-20.99760771310348</v>
+        <v>-22.86553984263139</v>
       </c>
       <c r="F33">
-        <v>-2.434886723688319</v>
+        <v>-1.908093929184598</v>
       </c>
       <c r="G33">
-        <v>-5.626932093222031</v>
+        <v>-5.949203769833463</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.44180380052258</v>
       </c>
       <c r="E34">
-        <v>-20.26162653195487</v>
+        <v>-21.76218167913652</v>
       </c>
       <c r="F34">
-        <v>-2.527101411335362</v>
+        <v>-2.201362497532513</v>
       </c>
       <c r="G34">
-        <v>-5.184974263729328</v>
+        <v>-5.665900524764792</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.76758136196034</v>
       </c>
       <c r="E35">
-        <v>-20.46347420389876</v>
+        <v>-21.12257548181915</v>
       </c>
       <c r="F35">
-        <v>-2.23057570235964</v>
+        <v>-2.183055577930644</v>
       </c>
       <c r="G35">
-        <v>-5.870353196179102</v>
+        <v>-5.945644933378747</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.99901586847211</v>
       </c>
       <c r="E36">
-        <v>-20.40589465689123</v>
+        <v>-21.95980881330526</v>
       </c>
       <c r="F36">
-        <v>-2.204170663028003</v>
+        <v>-2.358481427923703</v>
       </c>
       <c r="G36">
-        <v>-4.218990180825388</v>
+        <v>-5.772937083140508</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-12.14101649540689</v>
       </c>
       <c r="E37">
-        <v>-21.01800396003403</v>
+        <v>-21.25022863562137</v>
       </c>
       <c r="F37">
-        <v>-2.478848181754888</v>
+        <v>-2.167835983639008</v>
       </c>
       <c r="G37">
-        <v>-4.964356198446756</v>
+        <v>-5.398544177558791</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-12.20300672497312</v>
       </c>
       <c r="E38">
-        <v>-20.21933511319724</v>
+        <v>-21.20914179094978</v>
       </c>
       <c r="F38">
-        <v>-1.968693146536396</v>
+        <v>-2.254826986443998</v>
       </c>
       <c r="G38">
-        <v>-4.284962732331985</v>
+        <v>-5.172615997231229</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-12.18887746656466</v>
       </c>
       <c r="E39">
-        <v>-19.89552657927877</v>
+        <v>-21.36938184371119</v>
       </c>
       <c r="F39">
-        <v>-2.267161377071683</v>
+        <v>-2.41696168145914</v>
       </c>
       <c r="G39">
-        <v>-4.970596576788282</v>
+        <v>-4.517399445189754</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-12.10177159544244</v>
       </c>
       <c r="E40">
-        <v>-18.95316472370459</v>
+        <v>-20.95516685470359</v>
       </c>
       <c r="F40">
-        <v>-2.598104094898919</v>
+        <v>-2.352300978731416</v>
       </c>
       <c r="G40">
-        <v>-3.691223010954776</v>
+        <v>-4.634890706378488</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.94244456617626</v>
       </c>
       <c r="E41">
-        <v>-18.60276046193907</v>
+        <v>-21.08881570809196</v>
       </c>
       <c r="F41">
-        <v>-2.291902226291096</v>
+        <v>-2.356702923109893</v>
       </c>
       <c r="G41">
-        <v>-3.20475820723211</v>
+        <v>-4.099400033764756</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.71264062799917</v>
       </c>
       <c r="E42">
-        <v>-18.63081435841659</v>
+        <v>-20.02960110922386</v>
       </c>
       <c r="F42">
-        <v>-2.633988142420791</v>
+        <v>-2.581911168908995</v>
       </c>
       <c r="G42">
-        <v>-3.864556554299936</v>
+        <v>-4.129148595980647</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.41323103246264</v>
       </c>
       <c r="E43">
-        <v>-18.3617822460949</v>
+        <v>-19.40869750955817</v>
       </c>
       <c r="F43">
-        <v>-2.722414705934832</v>
+        <v>-2.376272274633628</v>
       </c>
       <c r="G43">
-        <v>-3.489365807243254</v>
+        <v>-3.965912216530263</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.04530989597598</v>
       </c>
       <c r="E44">
-        <v>-18.07487624686494</v>
+        <v>-18.76209481989895</v>
       </c>
       <c r="F44">
-        <v>-2.156870884328151</v>
+        <v>-2.579131996272602</v>
       </c>
       <c r="G44">
-        <v>-3.194316746601249</v>
+        <v>-4.401689257501147</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.61759747472046</v>
       </c>
       <c r="E45">
-        <v>-17.9410145551982</v>
+        <v>-18.62740441748881</v>
       </c>
       <c r="F45">
-        <v>-3.146327582480466</v>
+        <v>-2.788781845512323</v>
       </c>
       <c r="G45">
-        <v>-2.817967308605822</v>
+        <v>-4.119600982645388</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.14231244417565</v>
       </c>
       <c r="E46">
-        <v>-17.18470052575515</v>
+        <v>-18.4356959988481</v>
       </c>
       <c r="F46">
-        <v>-2.671321004530159</v>
+        <v>-2.465242247163907</v>
       </c>
       <c r="G46">
-        <v>-2.830719530023095</v>
+        <v>-4.089246590595811</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.639270475523134</v>
       </c>
       <c r="E47">
-        <v>-16.48093490869711</v>
+        <v>-18.64997886041705</v>
       </c>
       <c r="F47">
-        <v>-2.941797043790045</v>
+        <v>-2.874338115975665</v>
       </c>
       <c r="G47">
-        <v>-2.791138647555568</v>
+        <v>-4.146916293889915</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.1285324614113</v>
       </c>
       <c r="E48">
-        <v>-17.01931612652102</v>
+        <v>-17.32148308315683</v>
       </c>
       <c r="F48">
-        <v>-2.807440821260382</v>
+        <v>-3.147985145653467</v>
       </c>
       <c r="G48">
-        <v>-3.324378149202596</v>
+        <v>-3.23923753902362</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.638284867445984</v>
       </c>
       <c r="E49">
-        <v>-16.05569308548083</v>
+        <v>-18.33847871885143</v>
       </c>
       <c r="F49">
-        <v>-3.260802158975538</v>
+        <v>-3.136070737299002</v>
       </c>
       <c r="G49">
-        <v>-2.309844915965245</v>
+        <v>-3.700234315912672</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.19356101234262</v>
       </c>
       <c r="E50">
-        <v>-16.41524033626784</v>
+        <v>-17.94927449178819</v>
       </c>
       <c r="F50">
-        <v>-3.229092254796373</v>
+        <v>-3.118774425928549</v>
       </c>
       <c r="G50">
-        <v>-3.041094767407161</v>
+        <v>-3.046169833718863</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.819881854643703</v>
       </c>
       <c r="E51">
-        <v>-15.91435035475342</v>
+        <v>-16.57793935041542</v>
       </c>
       <c r="F51">
-        <v>-3.396573233029182</v>
+        <v>-3.32320473216323</v>
       </c>
       <c r="G51">
-        <v>-2.689213571492487</v>
+        <v>-3.201199370777394</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.534150279653836</v>
       </c>
       <c r="E52">
-        <v>-15.83795952671803</v>
+        <v>-17.31221782533714</v>
       </c>
       <c r="F52">
-        <v>-3.536193730403636</v>
+        <v>-3.113731325180305</v>
       </c>
       <c r="G52">
-        <v>-2.258551323379776</v>
+        <v>-3.500141632973582</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.346738668619555</v>
       </c>
       <c r="E53">
-        <v>-15.87617079039476</v>
+        <v>-16.61410827231468</v>
       </c>
       <c r="F53">
-        <v>-3.576818524571729</v>
+        <v>-3.067437184507452</v>
       </c>
       <c r="G53">
-        <v>-2.159754712851306</v>
+        <v>-3.625459023817153</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.261151110487666</v>
       </c>
       <c r="E54">
-        <v>-15.70863536600698</v>
+        <v>-16.9499897179376</v>
       </c>
       <c r="F54">
-        <v>-3.655234268022939</v>
+        <v>-3.522067581083696</v>
       </c>
       <c r="G54">
-        <v>-1.917465816468666</v>
+        <v>-3.747611533125182</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.273604966805371</v>
       </c>
       <c r="E55">
-        <v>-15.19194553867981</v>
+        <v>-16.30134468650092</v>
       </c>
       <c r="F55">
-        <v>-3.786706115256054</v>
+        <v>-3.397479466967845</v>
       </c>
       <c r="G55">
-        <v>-2.893616584723708</v>
+        <v>-3.172748542412897</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.37407209988626</v>
       </c>
       <c r="E56">
-        <v>-15.34486757744483</v>
+        <v>-16.33729624164781</v>
       </c>
       <c r="F56">
-        <v>-3.741796176513279</v>
+        <v>-3.772306604693191</v>
       </c>
       <c r="G56">
-        <v>-2.581167296727293</v>
+        <v>-3.203619379566601</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.543977425081851</v>
       </c>
       <c r="E57">
-        <v>-14.50738970836231</v>
+        <v>-15.88832521463134</v>
       </c>
       <c r="F57">
-        <v>-3.626921498562655</v>
+        <v>-3.542882797181242</v>
       </c>
       <c r="G57">
-        <v>-2.56964328770509</v>
+        <v>-3.289233397757693</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.766826574213065</v>
       </c>
       <c r="E58">
-        <v>-14.99458558447752</v>
+        <v>-15.92517340763176</v>
       </c>
       <c r="F58">
-        <v>-3.541554924234554</v>
+        <v>-3.601326602550956</v>
       </c>
       <c r="G58">
-        <v>-3.091534239243496</v>
+        <v>-3.242445457651173</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.021245473559707</v>
       </c>
       <c r="E59">
-        <v>-13.42474931345252</v>
+        <v>-15.62004030052092</v>
       </c>
       <c r="F59">
-        <v>-3.42301389215914</v>
+        <v>-3.425196640265516</v>
       </c>
       <c r="G59">
-        <v>-2.425108180006049</v>
+        <v>-3.37055363838435</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.287352845682413</v>
       </c>
       <c r="E60">
-        <v>-12.39441279333133</v>
+        <v>-15.21052133905927</v>
       </c>
       <c r="F60">
-        <v>-3.605428677929619</v>
+        <v>-3.674999942621138</v>
       </c>
       <c r="G60">
-        <v>-2.391843818427452</v>
+        <v>-3.076216345033289</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.540424327027576</v>
       </c>
       <c r="E61">
-        <v>-13.09036679272614</v>
+        <v>-14.94583203331094</v>
       </c>
       <c r="F61">
-        <v>-3.797858425599944</v>
+        <v>-3.797442585163739</v>
       </c>
       <c r="G61">
-        <v>-2.927288143403635</v>
+        <v>-3.763167786614217</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.760287763176633</v>
       </c>
       <c r="E62">
-        <v>-12.56730993094419</v>
+        <v>-15.38623971597891</v>
       </c>
       <c r="F62">
-        <v>-4.06078306761591</v>
+        <v>-3.809475450056804</v>
       </c>
       <c r="G62">
-        <v>-2.506335725357607</v>
+        <v>-3.474792785779382</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.929625787049229</v>
       </c>
       <c r="E63">
-        <v>-14.09119124773935</v>
+        <v>-15.39122103738734</v>
       </c>
       <c r="F63">
-        <v>-3.720748189175546</v>
+        <v>-3.852373284378179</v>
       </c>
       <c r="G63">
-        <v>-3.699582138441435</v>
+        <v>-3.760463070908632</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.036648376863866</v>
       </c>
       <c r="E64">
-        <v>-13.05116832171575</v>
+        <v>-14.42550584135561</v>
       </c>
       <c r="F64">
-        <v>-4.017115679977334</v>
+        <v>-3.988901486237983</v>
       </c>
       <c r="G64">
-        <v>-3.013335843060371</v>
+        <v>-3.20026248638978</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.071364898398999</v>
       </c>
       <c r="E65">
-        <v>-13.46294699170722</v>
+        <v>-15.39401057737607</v>
       </c>
       <c r="F65">
-        <v>-4.25884819872748</v>
+        <v>-3.677371558495353</v>
       </c>
       <c r="G65">
-        <v>-2.986705814742474</v>
+        <v>-3.239912890313631</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.026992277844863</v>
       </c>
       <c r="E66">
-        <v>-13.59413688370943</v>
+        <v>-14.90531124789031</v>
       </c>
       <c r="F66">
-        <v>-3.820158076083306</v>
+        <v>-3.918970710093649</v>
       </c>
       <c r="G66">
-        <v>-3.678480721174121</v>
+        <v>-3.173046491511431</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.904061930042825</v>
       </c>
       <c r="E67">
-        <v>-12.32702004314918</v>
+        <v>-14.64750069415963</v>
       </c>
       <c r="F67">
-        <v>-3.738814882230604</v>
+        <v>-3.895191595428886</v>
       </c>
       <c r="G67">
-        <v>-3.639263998715914</v>
+        <v>-3.571053518424771</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.708534432529101</v>
       </c>
       <c r="E68">
-        <v>-12.78144335287089</v>
+        <v>-14.48059472765892</v>
       </c>
       <c r="F68">
-        <v>-3.976682238679287</v>
+        <v>-3.900768164784532</v>
       </c>
       <c r="G68">
-        <v>-2.932598258448626</v>
+        <v>-3.757993403936336</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.4513080344503</v>
       </c>
       <c r="E69">
-        <v>-12.02838982471336</v>
+        <v>-14.10451401826991</v>
       </c>
       <c r="F69">
-        <v>-4.206371123760131</v>
+        <v>-3.938669286932221</v>
       </c>
       <c r="G69">
-        <v>-2.614630291038246</v>
+        <v>-3.216828456268293</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.140697049105759</v>
       </c>
       <c r="E70">
-        <v>-13.20289484334274</v>
+        <v>-14.56418582936651</v>
       </c>
       <c r="F70">
-        <v>-4.351520973548272</v>
+        <v>-3.960381624926999</v>
       </c>
       <c r="G70">
-        <v>-2.879593113819355</v>
+        <v>-3.519538119288172</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.789715888557241</v>
       </c>
       <c r="E71">
-        <v>-13.48270472380269</v>
+        <v>-14.98794684158228</v>
       </c>
       <c r="F71">
-        <v>-4.454781940511647</v>
+        <v>-4.348350811497758</v>
       </c>
       <c r="G71">
-        <v>-2.45512820695616</v>
+        <v>-2.93108202859164</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.411734524015383</v>
       </c>
       <c r="E72">
-        <v>-13.02712212473502</v>
+        <v>-14.55379750999291</v>
       </c>
       <c r="F72">
-        <v>-4.470896171598306</v>
+        <v>-4.344788831665721</v>
       </c>
       <c r="G72">
-        <v>-2.332426147088613</v>
+        <v>-3.05045367964668</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.023425306901395</v>
       </c>
       <c r="E73">
-        <v>-12.42151118179323</v>
+        <v>-14.14928251230974</v>
       </c>
       <c r="F73">
-        <v>-4.249426347888038</v>
+        <v>-4.048203480236997</v>
       </c>
       <c r="G73">
-        <v>-2.335812835175287</v>
+        <v>-3.192042401815769</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.637226423679053</v>
       </c>
       <c r="E74">
-        <v>-13.25193368837181</v>
+        <v>-14.39182305168656</v>
       </c>
       <c r="F74">
-        <v>-4.254390753733015</v>
+        <v>-4.288438310722881</v>
       </c>
       <c r="G74">
-        <v>-2.969014259380609</v>
+        <v>-2.67652425044046</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.264678454961359</v>
       </c>
       <c r="E75">
-        <v>-12.81129958200346</v>
+        <v>-14.88177676847245</v>
       </c>
       <c r="F75">
-        <v>-4.604810874302276</v>
+        <v>-4.323778949228516</v>
       </c>
       <c r="G75">
-        <v>-1.971997122591541</v>
+        <v>-2.567471569831328</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.917055353926419</v>
       </c>
       <c r="E76">
-        <v>-13.00760893023597</v>
+        <v>-15.3773820208199</v>
       </c>
       <c r="F76">
-        <v>-4.932252083117879</v>
+        <v>-4.505572459446896</v>
       </c>
       <c r="G76">
-        <v>-2.413789424807281</v>
+        <v>-2.276223015468406</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.603852610154131</v>
       </c>
       <c r="E77">
-        <v>-14.94264851608355</v>
+        <v>-15.51003008145258</v>
       </c>
       <c r="F77">
-        <v>-4.599683280078947</v>
+        <v>-4.551140121907494</v>
       </c>
       <c r="G77">
-        <v>-2.563154618448118</v>
+        <v>-2.898281143388541</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.331111035246141</v>
       </c>
       <c r="E78">
-        <v>-13.79725705684948</v>
+        <v>-16.00675386687994</v>
       </c>
       <c r="F78">
-        <v>-4.764237636277667</v>
+        <v>-4.641070172257617</v>
       </c>
       <c r="G78">
-        <v>-2.682009824399032</v>
+        <v>-2.626872688442471</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.098863159549145</v>
       </c>
       <c r="E79">
-        <v>-14.70990759445933</v>
+        <v>-16.85043121687896</v>
       </c>
       <c r="F79">
-        <v>-4.933701726072778</v>
+        <v>-4.760883576663732</v>
       </c>
       <c r="G79">
-        <v>-2.276722907844836</v>
+        <v>-2.431636575809492</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.907557185483371</v>
       </c>
       <c r="E80">
-        <v>-15.69156754747207</v>
+        <v>-17.5658214267147</v>
       </c>
       <c r="F80">
-        <v>-5.117187590895077</v>
+        <v>-4.846900419403029</v>
       </c>
       <c r="G80">
-        <v>-1.632371566263249</v>
+        <v>-2.292904854440794</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.753436070510493</v>
       </c>
       <c r="E81">
-        <v>-15.177295925265</v>
+        <v>-18.56881954925158</v>
       </c>
       <c r="F81">
-        <v>-5.084631095230251</v>
+        <v>-4.751258775810604</v>
       </c>
       <c r="G81">
-        <v>-2.004202109597571</v>
+        <v>-1.832437764838025</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.634343510940605</v>
       </c>
       <c r="E82">
-        <v>-17.38780258499917</v>
+        <v>-19.01531802945986</v>
       </c>
       <c r="F82">
-        <v>-5.143243059182733</v>
+        <v>-4.70622789542702</v>
       </c>
       <c r="G82">
-        <v>-2.050457051872268</v>
+        <v>-2.387821505597238</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.546278987294154</v>
       </c>
       <c r="E83">
-        <v>-19.08717585501358</v>
+        <v>-18.77204840576781</v>
       </c>
       <c r="F83">
-        <v>-5.030252088706074</v>
+        <v>-5.048608710352112</v>
       </c>
       <c r="G83">
-        <v>-2.267916856710375</v>
+        <v>-2.230335543748568</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.488057829915919</v>
       </c>
       <c r="E84">
-        <v>-18.17361509412818</v>
+        <v>-19.98163098406061</v>
       </c>
       <c r="F84">
-        <v>-5.49193106351274</v>
+        <v>-5.06220470453426</v>
       </c>
       <c r="G84">
-        <v>-1.610124700239347</v>
+        <v>-2.515502625955849</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.458050588366362</v>
       </c>
       <c r="E85">
-        <v>-19.39565097594207</v>
+        <v>-21.01018781389678</v>
       </c>
       <c r="F85">
-        <v>-5.646541697408254</v>
+        <v>-5.500679451653705</v>
       </c>
       <c r="G85">
-        <v>-1.728135717077747</v>
+        <v>-2.435728410096031</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.456263680498928</v>
       </c>
       <c r="E86">
-        <v>-19.95186079593418</v>
+        <v>-21.29934899318257</v>
       </c>
       <c r="F86">
-        <v>-6.086664067291868</v>
+        <v>-5.413265981473288</v>
       </c>
       <c r="G86">
-        <v>-2.339656378546382</v>
+        <v>-1.458687105090926</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.479269713785646</v>
       </c>
       <c r="E87">
-        <v>-21.8793061308709</v>
+        <v>-23.62664952604856</v>
       </c>
       <c r="F87">
-        <v>-5.831158283735374</v>
+        <v>-5.628020230649059</v>
       </c>
       <c r="G87">
-        <v>-2.101346757901945</v>
+        <v>-2.927562918683394</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.519537387699907</v>
       </c>
       <c r="E88">
-        <v>-23.11017253699975</v>
+        <v>-23.22960198200404</v>
       </c>
       <c r="F88">
-        <v>-5.712603169414112</v>
+        <v>-5.294677732455914</v>
       </c>
       <c r="G88">
-        <v>-1.746224537904325</v>
+        <v>-1.756490539621605</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.569038670822962</v>
       </c>
       <c r="E89">
-        <v>-24.41679125632891</v>
+        <v>-25.76265825988255</v>
       </c>
       <c r="F89">
-        <v>-6.069105991822129</v>
+        <v>-5.553669286043387</v>
       </c>
       <c r="G89">
-        <v>-2.240873010200068</v>
+        <v>-2.043312894598521</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.621458635116634</v>
       </c>
       <c r="E90">
-        <v>-25.99121487152368</v>
+        <v>-26.25032056882056</v>
       </c>
       <c r="F90">
-        <v>-5.684269690768757</v>
+        <v>-5.933684488812466</v>
       </c>
       <c r="G90">
-        <v>-2.023972687558099</v>
+        <v>-1.74542669642936</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.676253039482045</v>
       </c>
       <c r="E91">
-        <v>-26.99240160445749</v>
+        <v>-28.74462669461543</v>
       </c>
       <c r="F91">
-        <v>-6.191734188662957</v>
+        <v>-5.399947490371077</v>
       </c>
       <c r="G91">
-        <v>-1.594442646019819</v>
+        <v>-2.868426643715393</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.736346954601539</v>
       </c>
       <c r="E92">
-        <v>-28.55299978850685</v>
+        <v>-30.1441198873679</v>
       </c>
       <c r="F92">
-        <v>-5.798100625791854</v>
+        <v>-5.468100590069004</v>
       </c>
       <c r="G92">
-        <v>-2.331538920884089</v>
+        <v>-2.824985665149077</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.813423893066569</v>
       </c>
       <c r="E93">
-        <v>-31.72532262815215</v>
+        <v>-32.67863433387687</v>
       </c>
       <c r="F93">
-        <v>-5.819867636035217</v>
+        <v>-5.769579936113467</v>
       </c>
       <c r="G93">
-        <v>-2.596654028760004</v>
+        <v>-3.142831142374503</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.922667475412154</v>
       </c>
       <c r="E94">
-        <v>-33.9181682392564</v>
+        <v>-34.32377686341243</v>
       </c>
       <c r="F94">
-        <v>-6.167154042719687</v>
+        <v>-5.568715751547837</v>
       </c>
       <c r="G94">
-        <v>-2.491454823158583</v>
+        <v>-3.666973264879614</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.083654306231767</v>
       </c>
       <c r="E95">
-        <v>-34.08845018312983</v>
+        <v>-36.74399036173079</v>
       </c>
       <c r="F95">
-        <v>-5.686035770071526</v>
+        <v>-5.558237732269826</v>
       </c>
       <c r="G95">
-        <v>-3.474729885414136</v>
+        <v>-3.60562223494584</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.319245971631153</v>
       </c>
       <c r="E96">
-        <v>-38.18602177507432</v>
+        <v>-37.8562786759688</v>
       </c>
       <c r="F96">
-        <v>-6.059881292424554</v>
+        <v>-5.369842962218538</v>
       </c>
       <c r="G96">
-        <v>-3.501081827906735</v>
+        <v>-4.219725121935106</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.633004564783797</v>
       </c>
       <c r="E97">
-        <v>-39.6822861931337</v>
+        <v>-41.72369510494745</v>
       </c>
       <c r="F97">
-        <v>-6.013115810699508</v>
+        <v>-5.469580054250404</v>
       </c>
       <c r="G97">
-        <v>-4.374026338974997</v>
+        <v>-4.225809904636287</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.045050691643529</v>
       </c>
       <c r="E98">
-        <v>-42.15951544344565</v>
+        <v>-42.79927787311628</v>
       </c>
       <c r="F98">
-        <v>-5.886115490706705</v>
+        <v>-5.395354193122554</v>
       </c>
       <c r="G98">
-        <v>-4.408969147142004</v>
+        <v>-5.454227553529332</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.525562771762614</v>
       </c>
       <c r="E99">
-        <v>-44.46212673602182</v>
+        <v>-45.38633846777326</v>
       </c>
       <c r="F99">
-        <v>-6.551560421091006</v>
+        <v>-5.364913347804478</v>
       </c>
       <c r="G99">
-        <v>-5.071283508819676</v>
+        <v>-5.671263608538411</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.100993049155536</v>
       </c>
       <c r="E100">
-        <v>-46.88723098626848</v>
+        <v>-47.38938667626804</v>
       </c>
       <c r="F100">
-        <v>-5.870406331280015</v>
+        <v>-5.47931999817252</v>
       </c>
       <c r="G100">
-        <v>-6.17156980316077</v>
+        <v>-5.606529201063503</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.685136816120797</v>
       </c>
       <c r="E101">
-        <v>-49.19970529523336</v>
+        <v>-49.00278573512832</v>
       </c>
       <c r="F101">
-        <v>-6.276158495070373</v>
+        <v>-5.176546742244884</v>
       </c>
       <c r="G101">
-        <v>-5.311433792783948</v>
+        <v>-5.117968822014479</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.364822044560055</v>
       </c>
       <c r="E102">
-        <v>-51.46414947675439</v>
+        <v>-51.66868479802184</v>
       </c>
       <c r="F102">
-        <v>-6.154758352904195</v>
+        <v>-5.095729561692959</v>
       </c>
       <c r="G102">
-        <v>-6.24261411043353</v>
+        <v>-6.68340331735087</v>
       </c>
     </row>
   </sheetData>
